--- a/TestData/excel.xlsx
+++ b/TestData/excel.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sriram-HP\Documents\Playwright_ts\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8632B085-0E37-456D-A10D-1993AAE349FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{19C25F25-EA43-4926-857D-4B500CFC252D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="20">
   <si>
     <t>password</t>
   </si>
@@ -40,9 +40,6 @@
   </si>
   <si>
     <t>Rock_1986</t>
-  </si>
-  <si>
-    <t>ZARA COAT 3</t>
   </si>
   <si>
     <t>cvv</t>
@@ -426,22 +423,22 @@
         <v>1</v>
       </c>
       <c r="D1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
         <v>6</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
+        <v>16</v>
+      </c>
+      <c r="I1" t="s">
         <v>7</v>
-      </c>
-      <c r="H1" t="s">
-        <v>17</v>
-      </c>
-      <c r="I1" t="s">
-        <v>8</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.3">
@@ -452,10 +449,10 @@
         <v>4</v>
       </c>
       <c r="C2" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E2" s="1">
         <v>14</v>
@@ -464,13 +461,13 @@
         <v>123</v>
       </c>
       <c r="G2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I2" t="s">
         <v>9</v>
-      </c>
-      <c r="H2" t="s">
-        <v>18</v>
-      </c>
-      <c r="I2" t="s">
-        <v>10</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.3">
@@ -481,10 +478,10 @@
         <v>4</v>
       </c>
       <c r="C3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E3" s="1">
         <v>16</v>
@@ -493,13 +490,13 @@
         <v>345</v>
       </c>
       <c r="G3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H3" t="s">
+        <v>18</v>
+      </c>
+      <c r="I3" t="s">
         <v>19</v>
-      </c>
-      <c r="I3" t="s">
-        <v>20</v>
       </c>
     </row>
   </sheetData>

--- a/TestData/excel.xlsx
+++ b/TestData/excel.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sriram-HP\Documents\Playwright_ts\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{19C25F25-EA43-4926-857D-4B500CFC252D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E5B9EC9F-145A-4151-A9B5-D4DB0911BA93}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="17">
   <si>
     <t>password</t>
   </si>
@@ -66,25 +66,16 @@
     <t>08</t>
   </si>
   <si>
-    <t>07</t>
-  </si>
-  <si>
     <t>day</t>
   </si>
   <si>
-    <t>sri</t>
-  </si>
-  <si>
     <t>details</t>
   </si>
   <si>
     <t>ind</t>
   </si>
   <si>
-    <t>aus</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Australia</t>
+    <t>Rock_1987</t>
   </si>
 </sst>
 </file>
@@ -426,7 +417,7 @@
         <v>11</v>
       </c>
       <c r="E1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F1" t="s">
         <v>5</v>
@@ -435,7 +426,7 @@
         <v>6</v>
       </c>
       <c r="H1" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="I1" t="s">
         <v>7</v>
@@ -464,7 +455,7 @@
         <v>8</v>
       </c>
       <c r="H2" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="I2" t="s">
         <v>9</v>
@@ -475,28 +466,7 @@
         <v>3</v>
       </c>
       <c r="B3" t="s">
-        <v>4</v>
-      </c>
-      <c r="C3" t="s">
-        <v>10</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="E3" s="1">
         <v>16</v>
-      </c>
-      <c r="F3" s="1">
-        <v>345</v>
-      </c>
-      <c r="G3" t="s">
-        <v>15</v>
-      </c>
-      <c r="H3" t="s">
-        <v>18</v>
-      </c>
-      <c r="I3" t="s">
-        <v>19</v>
       </c>
     </row>
   </sheetData>

--- a/TestData/excel.xlsx
+++ b/TestData/excel.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29530"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sriram-HP\Documents\Playwright_ts\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E5B9EC9F-145A-4151-A9B5-D4DB0911BA93}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE8F85FE-6394-4263-A2A2-397B6399B018}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="19">
   <si>
     <t>password</t>
   </si>
@@ -75,7 +75,13 @@
     <t>ind</t>
   </si>
   <si>
-    <t>Rock_1987</t>
+    <t>aus</t>
+  </si>
+  <si>
+    <t>Australia</t>
+  </si>
+  <si>
+    <t>09</t>
   </si>
 </sst>
 </file>
@@ -466,7 +472,28 @@
         <v>3</v>
       </c>
       <c r="B3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E3" s="1">
+        <v>15</v>
+      </c>
+      <c r="F3">
+        <v>122</v>
+      </c>
+      <c r="G3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H3" t="s">
         <v>16</v>
+      </c>
+      <c r="I3" t="s">
+        <v>17</v>
       </c>
     </row>
   </sheetData>

--- a/TestData/excel.xlsx
+++ b/TestData/excel.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sriram-HP\Documents\Playwright_ts\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE8F85FE-6394-4263-A2A2-397B6399B018}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA9C0283-D08D-439F-ACF0-D6715CD34084}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -78,10 +78,10 @@
     <t>aus</t>
   </si>
   <si>
-    <t>Australia</t>
-  </si>
-  <si>
     <t>09</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Australia</t>
   </si>
 </sst>
 </file>
@@ -478,7 +478,7 @@
         <v>10</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E3" s="1">
         <v>15</v>
@@ -493,7 +493,7 @@
         <v>16</v>
       </c>
       <c r="I3" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
   </sheetData>
